--- a/mode_docx_gen/pmi_ka2/ka_modes/КА_30.xlsx
+++ b/mode_docx_gen/pmi_ka2/ka_modes/КА_30.xlsx
@@ -656,8 +656,8 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="2" t="n">
-        <v>1</v>
+      <c r="R2" t="n">
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1122,8 +1122,8 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
+      <c r="H2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1185,8 +1185,8 @@
       <c r="AB2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC2" s="2" t="n">
-        <v>1</v>
+      <c r="AC2" t="n">
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -1657,9 +1657,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AI2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
